--- a/ralph-lauren/boca/RL_Boca_CostPlus_CLIENT_2026-09-03.xlsx
+++ b/ralph-lauren/boca/RL_Boca_CostPlus_CLIENT_2026-09-03.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C13" s="78" t="inlineStr">
         <is>
-          <t>Ralph Lauren policy: net 90</t>
+          <t>LBC proposes net 30. Ralph Lauren stated policy: net 90.</t>
         </is>
       </c>
       <c r="D13" s="109" t="n"/>
@@ -1652,7 +1652,11 @@
         <f>H36*I36</f>
         <v/>
       </c>
-      <c r="K36" s="83" t="n"/>
+      <c r="K36" s="83" t="inlineStr">
+        <is>
+          <t>N/A — not used on this exhibit.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="B37" s="14" t="inlineStr">
@@ -1941,9 +1945,7 @@
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E48" s="17" t="n">
-        <v>3500</v>
-      </c>
+      <c r="E48" s="17"/>
       <c r="F48" s="20" t="inlineStr">
         <is>
           <t>Per Week</t>
@@ -1964,7 +1966,11 @@
         <f>E48*G48</f>
         <v/>
       </c>
-      <c r="K48" s="83" t="n"/>
+      <c r="K48" s="83" t="inlineStr">
+        <is>
+          <t>Open until a single figure is set.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="B49" s="14" t="inlineStr">
@@ -2703,7 +2709,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>Owner's representative: Charrette MG — Landis Kauffman, Claudia Mardones.  Payment: Ralph Lauren policy net 90.  Permit fees excluded / invoiced separately.  Sales tax invoiced separately.</t>
+          <t>Owner's representative: Charrette MG — Landis Kauffman, Claudia Mardones.  Payment: LBC proposes net 30 (Ralph Lauren stated policy is net 90).  Permit fees excluded / invoiced separately.  Sales tax invoiced separately.</t>
         </is>
       </c>
     </row>
@@ -2814,16 +2820,13 @@
     <row r="15">
       <c r="C15" s="40" t="inlineStr">
         <is>
-          <t>CO CM Fee % (follows project CM fee)</t>
-        </is>
-      </c>
-      <c r="E15" s="128">
-        <f>E12</f>
-        <v/>
-      </c>
+          <t>CO CM Fee % (open — separate from project CM fee)</t>
+        </is>
+      </c>
+      <c r="E15" s="128"/>
       <c r="G15" s="48" t="inlineStr">
         <is>
-          <t>Follows project CM fee.</t>
+          <t>Open — separate from the 10% project CM fee.</t>
         </is>
       </c>
     </row>

--- a/ralph-lauren/boca/RL_Boca_CostPlus_CLIENT_2026-09-03.xlsx
+++ b/ralph-lauren/boca/RL_Boca_CostPlus_CLIENT_2026-09-03.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C13" s="78" t="inlineStr">
         <is>
-          <t>LBC proposes net 30. Ralph Lauren stated policy: net 90.</t>
+          <t>Opening ask: net 30. If net 30 is not accepted, net 45 is a possible settlement band. Ralph Lauren stated policy: net 90.</t>
         </is>
       </c>
       <c r="D13" s="109" t="n"/>
@@ -2709,7 +2709,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>Owner's representative: Charrette MG — Landis Kauffman, Claudia Mardones.  Payment: LBC proposes net 30 (Ralph Lauren stated policy is net 90).  Permit fees excluded / invoiced separately.  Sales tax invoiced separately.</t>
+          <t>Owner's representative: Charrette MG — Landis Kauffman, Claudia Mardones.  Payment: opening ask net 30; net 45 is a possible settlement band if net 30 is not accepted (Ralph Lauren stated policy is net 90).  Permit fees excluded / invoiced separately.  Sales tax invoiced separately.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
     <row r="18">
       <c r="B18" s="42" t="inlineStr">
         <is>
-          <t>TRADE PACKAGES — amounts entered when bids are received</t>
+          <t>TRADE PACKAGES — TBD until bids are received (amounts stay blank for formula safety)</t>
         </is>
       </c>
     </row>
@@ -2879,9 +2879,7 @@
           <t>Trade package 1</t>
         </is>
       </c>
-      <c r="D20" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D20" s="52"/>
     </row>
     <row r="21">
       <c r="B21" s="53" t="n">
@@ -2892,9 +2890,7 @@
           <t>Trade package 2</t>
         </is>
       </c>
-      <c r="D21" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D21" s="55"/>
     </row>
     <row r="22">
       <c r="B22" s="50" t="n">
@@ -2905,9 +2901,7 @@
           <t>Trade package 3</t>
         </is>
       </c>
-      <c r="D22" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D22" s="52"/>
     </row>
     <row r="23">
       <c r="B23" s="53" t="n">
@@ -2918,9 +2912,7 @@
           <t>Trade package 4</t>
         </is>
       </c>
-      <c r="D23" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D23" s="55"/>
     </row>
     <row r="24">
       <c r="B24" s="50" t="n">
@@ -2931,9 +2923,7 @@
           <t>Trade package 5</t>
         </is>
       </c>
-      <c r="D24" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D24" s="52"/>
     </row>
     <row r="25">
       <c r="B25" s="53" t="n">
@@ -2944,9 +2934,7 @@
           <t>Trade package 6</t>
         </is>
       </c>
-      <c r="D25" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D25" s="55"/>
     </row>
     <row r="26">
       <c r="B26" s="50" t="n">
@@ -2957,9 +2945,7 @@
           <t>Trade package 7</t>
         </is>
       </c>
-      <c r="D26" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D26" s="52"/>
     </row>
     <row r="27">
       <c r="B27" s="53" t="n">
@@ -2970,9 +2956,7 @@
           <t>Trade package 8</t>
         </is>
       </c>
-      <c r="D27" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D27" s="55"/>
     </row>
     <row r="28">
       <c r="B28" s="50" t="n">
@@ -2983,9 +2967,7 @@
           <t>Trade package 9</t>
         </is>
       </c>
-      <c r="D28" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D28" s="52"/>
     </row>
     <row r="29">
       <c r="B29" s="53" t="n">
@@ -2996,9 +2978,7 @@
           <t>Trade package 10</t>
         </is>
       </c>
-      <c r="D29" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D29" s="55"/>
     </row>
     <row r="30">
       <c r="B30" s="50" t="n">
@@ -3009,9 +2989,7 @@
           <t>Trade package 11</t>
         </is>
       </c>
-      <c r="D30" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D30" s="52"/>
     </row>
     <row r="31">
       <c r="B31" s="53" t="n">
@@ -3022,9 +3000,7 @@
           <t>Trade package 12</t>
         </is>
       </c>
-      <c r="D31" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D31" s="55"/>
     </row>
     <row r="32">
       <c r="B32" s="50" t="n">
@@ -3035,9 +3011,7 @@
           <t>Trade package 13</t>
         </is>
       </c>
-      <c r="D32" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D32" s="52"/>
     </row>
     <row r="33">
       <c r="B33" s="53" t="n">
@@ -3048,9 +3022,7 @@
           <t>Trade package 14</t>
         </is>
       </c>
-      <c r="D33" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D33" s="55"/>
     </row>
     <row r="34">
       <c r="B34" s="50" t="n">
@@ -3061,9 +3033,7 @@
           <t>Trade package 15</t>
         </is>
       </c>
-      <c r="D34" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D34" s="52"/>
     </row>
     <row r="35">
       <c r="B35" s="53" t="n">
@@ -3074,9 +3044,7 @@
           <t>Trade package 16</t>
         </is>
       </c>
-      <c r="D35" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D35" s="55"/>
     </row>
     <row r="36">
       <c r="B36" s="50" t="n">
@@ -3087,9 +3055,7 @@
           <t>Trade package 17</t>
         </is>
       </c>
-      <c r="D36" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D36" s="52"/>
     </row>
     <row r="37">
       <c r="B37" s="53" t="n">
@@ -3100,9 +3066,7 @@
           <t>Trade package 18</t>
         </is>
       </c>
-      <c r="D37" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D37" s="55"/>
     </row>
     <row r="38">
       <c r="B38" s="50" t="n">
@@ -3113,9 +3077,7 @@
           <t>Trade package 19</t>
         </is>
       </c>
-      <c r="D38" s="52" t="n">
-        <v>0</v>
-      </c>
+      <c r="D38" s="52"/>
     </row>
     <row r="39">
       <c r="B39" s="53" t="n">
@@ -3126,9 +3088,7 @@
           <t>Trade package 20</t>
         </is>
       </c>
-      <c r="D39" s="55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D39" s="55"/>
     </row>
     <row r="40">
       <c r="C40" s="56" t="inlineStr">
@@ -3190,7 +3150,7 @@
       </c>
       <c r="G44" s="83" t="inlineStr">
         <is>
-          <t>Entered commercial terms. Trade-package rows are $0 until bids are received.</t>
+          <t>Entered commercial terms. Trade-package rows are TBD until bids are received. Blank amounts do not invent a job total.</t>
         </is>
       </c>
     </row>

--- a/ralph-lauren/boca/RL_Boca_CostPlus_CLIENT_2026-09-03.xlsx
+++ b/ralph-lauren/boca/RL_Boca_CostPlus_CLIENT_2026-09-03.xlsx
@@ -930,7 +930,7 @@
     <row r="5" ht="36" customHeight="1">
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>Commercial terms: 21 weeks · $4,400/wk superintendent · 10% CM fee · 1.5% liability insurance · 1% pre-construction, payable with first pay application / NTP.</t>
+          <t>Commercial terms: 21 weeks · $4,400/wk superintendent · $3,500/wk project manager (Shawn Rasmusen) + 4 trips · 5 months parking × $250 = $1,250 · 10% CM fee · 1.5% liability insurance · 1% pre-construction, payable with first pay application / NTP.</t>
         </is>
       </c>
     </row>
@@ -1945,13 +1945,17 @@
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E48" s="17"/>
+      <c r="E48" s="17" t="n">
+        <v>3500</v>
+      </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
           <t>Per Week</t>
         </is>
       </c>
-      <c r="G48" s="39" t="n"/>
+      <c r="G48" s="39" t="n">
+        <v>21</v>
+      </c>
       <c r="H48" s="20" t="inlineStr">
         <is>
           <t>Weeks</t>
@@ -1968,7 +1972,7 @@
       </c>
       <c r="K48" s="83" t="inlineStr">
         <is>
-          <t>Open until a single figure is set.</t>
+          <t>Shawn Rasmusen. $3,500 per week × 21 weeks + 4 trips.</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="G11" s="83" t="inlineStr">
         <is>
-          <t>$4,400 per week superintendent.</t>
+          <t>$4,400 per week superintendent. Project manager $3,500/wk (Shawn Rasmusen) + 4 trips — see GC bid form C-5.</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3161,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="B46" s="60" t="inlineStr">
         <is>
-          <t>Cost-plus CM fee form. Duration 21 weeks. Superintendent $4,400/wk. CM fee 10%. Insurance 1.5%. Pre-construction 1% of project total, payable with first pay application / NTP.</t>
+          <t>Cost-plus CM fee form. Duration 21 weeks. Superintendent $4,400/wk. Project manager $3,500/wk + 4 trips. Parking 5 months × $250 = $1,250. CM fee 10%. Insurance 1.5%. Pre-construction 1% of project total, payable with first pay application / NTP.</t>
         </is>
       </c>
     </row>
@@ -3385,19 +3389,21 @@
           <t>$/month</t>
         </is>
       </c>
-      <c r="E10" s="99" t="n"/>
+      <c r="E10" s="99" t="n">
+        <v>5</v>
+      </c>
       <c r="F10" s="95">
         <f>IF(E10="","",C10*E10)</f>
         <v/>
       </c>
       <c r="G10" s="90" t="inlineStr">
         <is>
-          <t>Qty pending</t>
+          <t>Set — 5 months</t>
         </is>
       </c>
       <c r="H10" s="97" t="inlineStr">
         <is>
-          <t>$250 per month. Month count to be confirmed.</t>
+          <t>$250 × 5 months = $1,250 (from 21-week duration).</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3506,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="B17" s="103" t="inlineStr">
         <is>
-          <t>Parking months and sprinkler-shutdown count to be confirmed. Permit fees and sales tax invoiced separately.</t>
+          <t>Parking is set at 5 months × $250 = $1,250. Sprinkler-shutdown count still Open / TBD. Permit fees and sales tax invoiced separately.</t>
         </is>
       </c>
     </row>
